--- a/tools/importer/reports/import-story-hub.report.xlsx
+++ b/tools/importer/reports/import-story-hub.report.xlsx
@@ -52,7 +52,7 @@
     <t>company-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:15.426Z</t>
+    <t>2026-03-06T14:58:06.089Z</t>
   </si>
   <si>
     <t>Our Company | About UPS</t>
@@ -73,7 +73,7 @@
     <t>story-hub</t>
   </si>
   <si>
-    <t>2026-03-06T14:39:42.372Z</t>
+    <t>2026-03-06T14:59:29.310Z</t>
   </si>
   <si>
     <t>Our Stories | About UPS</t>
@@ -94,7 +94,7 @@
     <t>company-culture</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:19.704Z</t>
+    <t>2026-03-06T14:40:11.991Z</t>
   </si>
   <si>
     <t>Our Culture</t>
@@ -115,7 +115,7 @@
     <t>company-strategy</t>
   </si>
   <si>
-    <t>2026-03-06T14:21:12.153Z</t>
+    <t>2026-03-06T14:40:08.818Z</t>
   </si>
   <si>
     <t>Our Strategy | About UPS</t>
@@ -136,7 +136,7 @@
     <t>story-category</t>
   </si>
   <si>
-    <t>2026-03-06T14:20:46.900Z</t>
+    <t>2026-03-06T14:39:45.703Z</t>
   </si>
   <si>
     <t>Customer First | About UPS</t>
@@ -151,7 +151,7 @@
     <t>us/en/our-stories/innovation-driven</t>
   </si>
   <si>
-    <t>2026-03-06T14:20:57.039Z</t>
+    <t>2026-03-06T14:40:01.461Z</t>
   </si>
   <si>
     <t>Innovation Driven | About UPS</t>
@@ -166,7 +166,7 @@
     <t>us/en/our-stories/people-led</t>
   </si>
   <si>
-    <t>2026-03-06T14:20:52.704Z</t>
+    <t>2026-03-06T14:39:52.892Z</t>
   </si>
   <si>
     <t>People Led | About UPS</t>
